--- a/administrative_forms/015_road_traffic_incident_form--administrative_forms.xlsx
+++ b/administrative_forms/015_road_traffic_incident_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'not_involved',_'label':_'not_involved'}</t>
+          <t>not_involved</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Not Involved', 'label': 'Not Involved'}</t>
+          <t>Not Involved</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'witness',_'label':_'witness'}</t>
+          <t>witness</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Witness', 'label': 'Witness'}</t>
+          <t>Witness</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'driver',_'label':_'driver'}</t>
+          <t>driver</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Driver', 'label': 'Driver'}</t>
+          <t>Driver</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'passenger',_'label':_'passenger'}</t>
+          <t>passenger</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Passenger', 'label': 'Passenger'}</t>
+          <t>Passenger</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'both',_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Both', 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'none',_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'None', 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'light',_'label':_'light'}</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Light', 'label': 'Light'}</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'minor',_'label':_'minor'}</t>
+          <t>minor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Minor', 'label': 'Minor'}</t>
+          <t>Minor</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'major',_'label':_'major'}</t>
+          <t>major</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Major', 'label': 'Major'}</t>
+          <t>Major</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'total',_'label':_'total'}</t>
+          <t>total</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Total', 'label': 'Total'}</t>
+          <t>Total</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'partial',_'label':_'partial'}</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Partial', 'label': 'Partial'}</t>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'moderate',_'label':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Moderate', 'label': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'severe',_'label':_'severe'}</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'Severe', 'label': 'Severe'}</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'extensive',_'label':_'extensive'}</t>
+          <t>extensive</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'Extensive', 'label': 'Extensive'}</t>
+          <t>Extensive</t>
         </is>
       </c>
     </row>
